--- a/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
+++ b/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\endo-learn\BCSG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/endo-learn/BCSG/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6555E788-9D4D-E240-9EA9-9A2E9BD4C033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22635" windowHeight="13365"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="BCSG" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -159,7 +171,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#\ ##0"/>
   </numFmts>
@@ -259,7 +271,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -843,19 +855,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="38.73046875" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -863,69 +875,69 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="12">
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -933,23 +945,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A15:AN27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A15:BF27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
     <col min="3" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:1" ht="24" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:58" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1064,8 +1076,68 @@
       <c r="AL17" s="4">
         <v>2050</v>
       </c>
+      <c r="AM17">
+        <v>2051</v>
+      </c>
+      <c r="AN17">
+        <v>2052</v>
+      </c>
+      <c r="AO17">
+        <v>2053</v>
+      </c>
+      <c r="AP17">
+        <v>2054</v>
+      </c>
+      <c r="AQ17">
+        <v>2055</v>
+      </c>
+      <c r="AR17">
+        <v>2056</v>
+      </c>
+      <c r="AS17">
+        <v>2057</v>
+      </c>
+      <c r="AT17">
+        <v>2058</v>
+      </c>
+      <c r="AU17">
+        <v>2059</v>
+      </c>
+      <c r="AV17">
+        <v>2060</v>
+      </c>
+      <c r="AW17">
+        <v>2061</v>
+      </c>
+      <c r="AX17">
+        <v>2062</v>
+      </c>
+      <c r="AY17">
+        <v>2063</v>
+      </c>
+      <c r="AZ17">
+        <v>2064</v>
+      </c>
+      <c r="BA17">
+        <v>2065</v>
+      </c>
+      <c r="BB17">
+        <v>2066</v>
+      </c>
+      <c r="BC17">
+        <v>2067</v>
+      </c>
+      <c r="BD17">
+        <v>2068</v>
+      </c>
+      <c r="BE17">
+        <v>2069</v>
+      </c>
+      <c r="BF17">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1283,7 @@
         <v>645.25886199836145</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>5</v>
       </c>
@@ -1357,7 +1429,7 @@
         <v>140.98274447844116</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>6</v>
       </c>
@@ -1503,7 +1575,7 @@
         <v>133.61743935810051</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>7</v>
       </c>
@@ -1648,8 +1720,88 @@
       <c r="AL21" s="10">
         <v>919.8590458349031</v>
       </c>
+      <c r="AM21" s="9">
+        <f>_xlfn.FORECAST.LINEAR(AM17,$B$21:$AL$21,$B$17:$AL$17)</f>
+        <v>867.79701259917056</v>
+      </c>
+      <c r="AN21" s="9">
+        <f>_xlfn.FORECAST.LINEAR(AN17,$B$21:$AL$21,$B$17:$AL$17)</f>
+        <v>891.17565428673697</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" ref="AO21:BF21" si="15">_xlfn.FORECAST.LINEAR(AO17,$B$21:$AL$21,$B$17:$AL$17)</f>
+        <v>914.55429597431066</v>
+      </c>
+      <c r="AP21" s="9">
+        <f t="shared" si="15"/>
+        <v>937.93293766187708</v>
+      </c>
+      <c r="AQ21" s="9">
+        <f t="shared" si="15"/>
+        <v>961.31157934944349</v>
+      </c>
+      <c r="AR21" s="9">
+        <f t="shared" si="15"/>
+        <v>984.69022103700991</v>
+      </c>
+      <c r="AS21" s="9">
+        <f t="shared" si="15"/>
+        <v>1008.0688627245763</v>
+      </c>
+      <c r="AT21" s="9">
+        <f t="shared" si="15"/>
+        <v>1031.4475044121427</v>
+      </c>
+      <c r="AU21" s="9">
+        <f t="shared" si="15"/>
+        <v>1054.8261460997091</v>
+      </c>
+      <c r="AV21" s="9">
+        <f t="shared" si="15"/>
+        <v>1078.2047877872756</v>
+      </c>
+      <c r="AW21" s="9">
+        <f t="shared" si="15"/>
+        <v>1101.583429474842</v>
+      </c>
+      <c r="AX21" s="9">
+        <f t="shared" si="15"/>
+        <v>1124.9620711624084</v>
+      </c>
+      <c r="AY21" s="9">
+        <f t="shared" si="15"/>
+        <v>1148.3407128499821</v>
+      </c>
+      <c r="AZ21" s="9">
+        <f t="shared" si="15"/>
+        <v>1171.7193545375485</v>
+      </c>
+      <c r="BA21" s="9">
+        <f t="shared" si="15"/>
+        <v>1195.0979962251149</v>
+      </c>
+      <c r="BB21" s="9">
+        <f t="shared" si="15"/>
+        <v>1218.4766379126813</v>
+      </c>
+      <c r="BC21" s="9">
+        <f t="shared" si="15"/>
+        <v>1241.8552796002477</v>
+      </c>
+      <c r="BD21" s="9">
+        <f t="shared" si="15"/>
+        <v>1265.2339212878142</v>
+      </c>
+      <c r="BE21" s="9">
+        <f t="shared" si="15"/>
+        <v>1288.6125629753806</v>
+      </c>
+      <c r="BF21" s="9">
+        <f t="shared" si="15"/>
+        <v>1311.991204662947</v>
+      </c>
     </row>
-    <row r="23" spans="1:40" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:58" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1765,7 +1917,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>4</v>
       </c>
@@ -1777,39 +1929,39 @@
         <v>0.14857530142629291</v>
       </c>
       <c r="D24" s="5">
-        <f t="shared" ref="D24:L24" si="15">C24+($M24-$B24)/11</f>
+        <f t="shared" ref="D24:L24" si="16">C24+($M24-$B24)/11</f>
         <v>0.29715060285258582</v>
       </c>
       <c r="E24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.4457259042788787</v>
       </c>
       <c r="F24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.59430120570517164</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.74287650713146458</v>
       </c>
       <c r="H24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.89145180855775752</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.0400271099840503</v>
       </c>
       <c r="J24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.1886024114103433</v>
       </c>
       <c r="K24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.3371777128366362</v>
       </c>
       <c r="L24" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.4857530142629292</v>
       </c>
       <c r="M24" s="6">
@@ -1820,15 +1972,15 @@
         <v>1.8064832144336842</v>
       </c>
       <c r="O24" s="5">
-        <f t="shared" ref="O24:Q24" si="16">N24+($R24-$M24)/5</f>
+        <f t="shared" ref="O24:Q24" si="17">N24+($R24-$M24)/5</f>
         <v>1.9786381131781465</v>
       </c>
       <c r="P24" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.1507930119226089</v>
       </c>
       <c r="Q24" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.3229479106670712</v>
       </c>
       <c r="R24" s="6">
@@ -1839,15 +1991,15 @@
         <v>2.6371169750948549</v>
       </c>
       <c r="T24" s="5">
-        <f t="shared" ref="T24:V24" si="17">S24+($W24-$R24)/5</f>
+        <f t="shared" ref="T24:V24" si="18">S24+($W24-$R24)/5</f>
         <v>2.7791311407781762</v>
       </c>
       <c r="U24" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.9211453064614976</v>
       </c>
       <c r="V24" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.063159472144819</v>
       </c>
       <c r="W24" s="6">
@@ -1858,15 +2010,15 @@
         <v>3.7679835158923325</v>
       </c>
       <c r="Y24" s="5">
-        <f t="shared" ref="Y24:AA24" si="18">X24+($AB24-$W24)/5</f>
+        <f t="shared" ref="Y24:AA24" si="19">X24+($AB24-$W24)/5</f>
         <v>4.3307933939565251</v>
       </c>
       <c r="Z24" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4.8936032720207177</v>
       </c>
       <c r="AA24" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.4564131500849102</v>
       </c>
       <c r="AB24" s="6">
@@ -1877,15 +2029,15 @@
         <v>6.635810567326673</v>
       </c>
       <c r="AD24" s="5">
-        <f t="shared" ref="AD24:AF24" si="19">AC24+($AG24-$AB24)/5</f>
+        <f t="shared" ref="AD24:AF24" si="20">AC24+($AG24-$AB24)/5</f>
         <v>7.2523981065042431</v>
       </c>
       <c r="AE24" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.8689856456818132</v>
       </c>
       <c r="AF24" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.4855731848593834</v>
       </c>
       <c r="AG24" s="6">
@@ -1896,15 +2048,15 @@
         <v>9.8172559030086024</v>
       </c>
       <c r="AI24" s="5">
-        <f t="shared" ref="AI24:AK24" si="20">AH24+($AL24-$AG24)/5</f>
+        <f t="shared" ref="AI24:AK24" si="21">AH24+($AL24-$AG24)/5</f>
         <v>10.532351081980252</v>
       </c>
       <c r="AJ24" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11.247446260951902</v>
       </c>
       <c r="AK24" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11.962541439923552</v>
       </c>
       <c r="AL24" s="6">
@@ -1913,7 +2065,7 @@
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>5</v>
       </c>
@@ -1921,138 +2073,138 @@
         <v>0</v>
       </c>
       <c r="C25" s="5">
-        <f t="shared" ref="C25:L26" si="21">B25+($M25-$B25)/11</f>
+        <f t="shared" ref="C25:L26" si="22">B25+($M25-$B25)/11</f>
         <v>0</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M25" s="6">
         <v>0</v>
       </c>
       <c r="N25" s="5">
-        <f t="shared" ref="N25:Q26" si="22">M25+($R25-$M25)/5</f>
+        <f t="shared" ref="N25:Q26" si="23">M25+($R25-$M25)/5</f>
         <v>0</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P25" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="Q25" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R25" s="6">
         <v>0</v>
       </c>
       <c r="S25" s="5">
-        <f t="shared" ref="S25:V26" si="23">R25+($W25-$R25)/5</f>
+        <f t="shared" ref="S25:V26" si="24">R25+($W25-$R25)/5</f>
         <v>0</v>
       </c>
       <c r="T25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="W25" s="6">
         <v>0</v>
       </c>
       <c r="X25" s="5">
-        <f t="shared" ref="X25:AA26" si="24">W25+($AB25-$W25)/5</f>
+        <f t="shared" ref="X25:AA26" si="25">W25+($AB25-$W25)/5</f>
         <v>0.4817390168080295</v>
       </c>
       <c r="Y25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.96347803361605899</v>
       </c>
       <c r="Z25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.4452170504240884</v>
       </c>
       <c r="AA25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.926956067232118</v>
       </c>
       <c r="AB25" s="6">
         <v>2.4086950840401475</v>
       </c>
       <c r="AC25" s="5">
-        <f t="shared" ref="AC25:AF26" si="25">AB25+($AG25-$AB25)/5</f>
+        <f t="shared" ref="AC25:AF26" si="26">AB25+($AG25-$AB25)/5</f>
         <v>3.2625662153721953</v>
       </c>
       <c r="AD25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4.1164373467042426</v>
       </c>
       <c r="AE25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4.9703084780362898</v>
       </c>
       <c r="AF25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.8241796093683371</v>
       </c>
       <c r="AG25" s="6">
         <v>6.6780507407003853</v>
       </c>
       <c r="AH25" s="5">
-        <f t="shared" ref="AH25:AK26" si="26">AG25+($AL25-$AG25)/5</f>
+        <f t="shared" ref="AH25:AK26" si="27">AG25+($AL25-$AG25)/5</f>
         <v>7.5297571058200337</v>
       </c>
       <c r="AI25" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.381463470939682</v>
       </c>
       <c r="AJ25" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.2331698360593304</v>
       </c>
       <c r="AK25" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10.084876201178979</v>
       </c>
       <c r="AL25" s="6">
@@ -2061,7 +2213,7 @@
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>6</v>
       </c>
@@ -2069,138 +2221,138 @@
         <v>0</v>
       </c>
       <c r="C26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14090538734197408</v>
       </c>
       <c r="D26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.28181077468394816</v>
       </c>
       <c r="E26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.42271616202592222</v>
       </c>
       <c r="F26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.56362154936789632</v>
       </c>
       <c r="G26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.70452693670987043</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.84543232405184454</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.98633771139381865</v>
       </c>
       <c r="J26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.1272430987357926</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.2681484860777668</v>
       </c>
       <c r="L26" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.4090538734197409</v>
       </c>
       <c r="M26" s="8">
         <v>1.5499592607617148</v>
       </c>
       <c r="N26" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.6690823191699637</v>
       </c>
       <c r="O26" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.7882053775782127</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.9073284359864617</v>
       </c>
       <c r="Q26" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.0264514943947107</v>
       </c>
       <c r="R26" s="8">
         <v>2.1455745528029602</v>
       </c>
       <c r="S26" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3.7520168343362048</v>
       </c>
       <c r="T26" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.358459115869449</v>
       </c>
       <c r="U26" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.9649013974026932</v>
       </c>
       <c r="V26" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.5713436789359374</v>
       </c>
       <c r="W26" s="8">
         <v>10.177785960469183</v>
       </c>
       <c r="X26" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>10.614306661478681</v>
       </c>
       <c r="Y26" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11.050827362488178</v>
       </c>
       <c r="Z26" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11.487348063497675</v>
       </c>
       <c r="AA26" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11.923868764507173</v>
       </c>
       <c r="AB26" s="8">
         <v>12.360389465516672</v>
       </c>
       <c r="AC26" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12.734773208069678</v>
       </c>
       <c r="AD26" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.109156950622683</v>
       </c>
       <c r="AE26" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.483540693175689</v>
       </c>
       <c r="AF26" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.857924435728695</v>
       </c>
       <c r="AG26" s="8">
         <v>14.232308178281704</v>
       </c>
       <c r="AH26" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15.401083338169871</v>
       </c>
       <c r="AI26" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16.569858498058036</v>
       </c>
       <c r="AJ26" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17.738633657946203</v>
       </c>
       <c r="AK26" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18.907408817834369</v>
       </c>
       <c r="AL26" s="8">
@@ -2209,7 +2361,7 @@
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>7</v>
       </c>
@@ -2221,134 +2373,134 @@
         <v>0.28948068876826699</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" ref="D27:AK27" si="27">SUM(D24:D26)</f>
+        <f t="shared" ref="D27:AK27" si="28">SUM(D24:D26)</f>
         <v>0.57896137753653398</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.86844206630480092</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.157922755073068</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.447403443841335</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.7368841326096021</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2.0263648213778689</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2.3158455101461359</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2.605326198914403</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2.89480688768267</v>
       </c>
       <c r="M27" s="10">
         <v>3.1842875764509366</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3.4755655336036479</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3.7668434907563593</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4.0581214479090706</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4.3493994050617815</v>
       </c>
       <c r="R27" s="10">
         <v>4.6406773622144932</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6.3891338094310601</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.1375902566476253</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>9.8860467038641904</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>11.634503151080757</v>
       </c>
       <c r="W27" s="10">
         <v>13.382959598297322</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>14.864029194179043</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>16.34509879006076</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>17.826168385942481</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>19.307237981824201</v>
       </c>
       <c r="AB27" s="10">
         <v>20.788307577705922</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>22.633149990768544</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>24.47799240383117</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>26.322834816893792</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>28.167677229956414</v>
       </c>
       <c r="AG27" s="10">
         <v>30.01251964301904</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>32.748096346998508</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>35.48367305097797</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>38.219249754957431</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>40.9548264589369</v>
       </c>
       <c r="AL27" s="10">
@@ -2364,17 +2516,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BD2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43.3984375" customWidth="1"/>
+    <col min="1" max="1" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.2">
       <c r="B1">
         <v>2016</v>
       </c>
@@ -2480,8 +2632,68 @@
       <c r="AJ1">
         <v>2050</v>
       </c>
+      <c r="AK1">
+        <v>2051</v>
+      </c>
+      <c r="AL1">
+        <v>2052</v>
+      </c>
+      <c r="AM1">
+        <v>2053</v>
+      </c>
+      <c r="AN1">
+        <v>2054</v>
+      </c>
+      <c r="AO1">
+        <v>2055</v>
+      </c>
+      <c r="AP1">
+        <v>2056</v>
+      </c>
+      <c r="AQ1">
+        <v>2057</v>
+      </c>
+      <c r="AR1">
+        <v>2058</v>
+      </c>
+      <c r="AS1">
+        <v>2059</v>
+      </c>
+      <c r="AT1">
+        <v>2060</v>
+      </c>
+      <c r="AU1">
+        <v>2061</v>
+      </c>
+      <c r="AV1">
+        <v>2062</v>
+      </c>
+      <c r="AW1">
+        <v>2063</v>
+      </c>
+      <c r="AX1">
+        <v>2064</v>
+      </c>
+      <c r="AY1">
+        <v>2065</v>
+      </c>
+      <c r="AZ1">
+        <v>2066</v>
+      </c>
+      <c r="BA1">
+        <v>2067</v>
+      </c>
+      <c r="BB1">
+        <v>2068</v>
+      </c>
+      <c r="BC1">
+        <v>2069</v>
+      </c>
+      <c r="BD1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:56" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
@@ -2624,6 +2836,86 @@
       <c r="AJ2" s="11">
         <f>Data!AL21*10^6</f>
         <v>919859045.83490312</v>
+      </c>
+      <c r="AK2" s="11">
+        <f>Data!AM21*10^6</f>
+        <v>867797012.59917057</v>
+      </c>
+      <c r="AL2" s="11">
+        <f>Data!AN21*10^6</f>
+        <v>891175654.28673697</v>
+      </c>
+      <c r="AM2" s="11">
+        <f>Data!AO21*10^6</f>
+        <v>914554295.97431064</v>
+      </c>
+      <c r="AN2" s="11">
+        <f>Data!AP21*10^6</f>
+        <v>937932937.66187704</v>
+      </c>
+      <c r="AO2" s="11">
+        <f>Data!AQ21*10^6</f>
+        <v>961311579.34944344</v>
+      </c>
+      <c r="AP2" s="11">
+        <f>Data!AR21*10^6</f>
+        <v>984690221.03700995</v>
+      </c>
+      <c r="AQ2" s="11">
+        <f>Data!AS21*10^6</f>
+        <v>1008068862.7245764</v>
+      </c>
+      <c r="AR2" s="11">
+        <f>Data!AT21*10^6</f>
+        <v>1031447504.4121428</v>
+      </c>
+      <c r="AS2" s="11">
+        <f>Data!AU21*10^6</f>
+        <v>1054826146.0997092</v>
+      </c>
+      <c r="AT2" s="11">
+        <f>Data!AV21*10^6</f>
+        <v>1078204787.7872756</v>
+      </c>
+      <c r="AU2" s="11">
+        <f>Data!AW21*10^6</f>
+        <v>1101583429.4748421</v>
+      </c>
+      <c r="AV2" s="11">
+        <f>Data!AX21*10^6</f>
+        <v>1124962071.1624084</v>
+      </c>
+      <c r="AW2" s="11">
+        <f>Data!AY21*10^6</f>
+        <v>1148340712.849982</v>
+      </c>
+      <c r="AX2" s="11">
+        <f>Data!AZ21*10^6</f>
+        <v>1171719354.5375485</v>
+      </c>
+      <c r="AY2" s="11">
+        <f>Data!BA21*10^6</f>
+        <v>1195097996.2251148</v>
+      </c>
+      <c r="AZ2" s="11">
+        <f>Data!BB21*10^6</f>
+        <v>1218476637.9126813</v>
+      </c>
+      <c r="BA2" s="11">
+        <f>Data!BC21*10^6</f>
+        <v>1241855279.6002479</v>
+      </c>
+      <c r="BB2" s="11">
+        <f>Data!BD21*10^6</f>
+        <v>1265233921.2878141</v>
+      </c>
+      <c r="BC2" s="11">
+        <f>Data!BE21*10^6</f>
+        <v>1288612562.9753807</v>
+      </c>
+      <c r="BD2" s="11">
+        <f>Data!BF21*10^6</f>
+        <v>1311991204.6629469</v>
       </c>
     </row>
   </sheetData>
